--- a/src/fastcashflow/sample_data/sample_paa_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_paa_basis.xlsx
@@ -6004,12 +6004,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>expense_type</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>basis</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D3" t="n">
